--- a/config/xlsx/shop.xlsx
+++ b/config/xlsx/shop.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -457,7 +457,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>21</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>10</v>
@@ -465,7 +465,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>22</v>
+        <v>1002</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>30</v>
@@ -473,31 +473,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>23</v>
+        <v>2001</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>24</v>
+        <v>2002</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>31</v>
+        <v>5001</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>41</v>
+        <v>5002</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>20</v>
@@ -505,15 +505,15 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>42</v>
+        <v>7001</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>61</v>
+        <v>9001</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>6</v>
@@ -521,9 +521,65 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>65</v>
+        <v>1005</v>
       </c>
       <c r="B10" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>5005</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>27001</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>27051</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>28001</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15101</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>15201</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>20</v>
       </c>
     </row>
